--- a/data/trans_orig/P5703-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5703-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2007</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371972</t>
+          <t>372289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>432179</t>
+          <t>432791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>468653</t>
+          <t>470092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>539855</t>
+          <t>535834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>858304</t>
+          <t>859428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>951119</t>
+          <t>956722</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269014</t>
+          <t>271417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>328729</t>
+          <t>327500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305338</t>
+          <t>304279</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>367453</t>
+          <t>367263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588516</t>
+          <t>587909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>673352</t>
+          <t>676000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199908</t>
+          <t>200295</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>250378</t>
+          <t>252398</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>263475</t>
+          <t>264993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>328118</t>
+          <t>324929</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>481732</t>
+          <t>481202</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>559654</t>
+          <t>563371</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80724</t>
+          <t>81180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120328</t>
+          <t>119429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>124054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167491</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>214667</t>
+          <t>212733</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272203</t>
+          <t>272188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26530</t>
+          <t>26363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>51134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,47 +1235,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>47323</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>34141</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>62685</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>47323</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>35106</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>64397</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>802032</t>
+          <t>801028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>885069</t>
+          <t>882748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>711866</t>
+          <t>712754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>789563</t>
+          <t>789575</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1536282</t>
+          <t>1533729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1655205</t>
+          <t>1649228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>443908</t>
+          <t>441168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515660</t>
+          <t>516161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>380823</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449013</t>
+          <t>450005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>842223</t>
+          <t>843230</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>943738</t>
+          <t>943611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>247024</t>
+          <t>241901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>308877</t>
+          <t>303620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252836</t>
+          <t>248247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>311820</t>
+          <t>308786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>509937</t>
+          <t>507284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>593782</t>
+          <t>594815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67658</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100915</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98174</t>
+          <t>99977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141382</t>
+          <t>141617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172613</t>
+          <t>173665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227975</t>
+          <t>229860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35230</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259804</t>
+          <t>258447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>307000</t>
+          <t>306146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>244220</t>
+          <t>244131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>287429</t>
+          <t>287181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>515755</t>
+          <t>514659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>580958</t>
+          <t>582232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,74%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127263</t>
+          <t>125381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168287</t>
+          <t>167270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111456</t>
+          <t>111885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151835</t>
+          <t>150395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247419</t>
+          <t>245643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>306893</t>
+          <t>308048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106897</t>
+          <t>107733</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40367</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68006</t>
+          <t>69118</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118976</t>
+          <t>118930</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164055</t>
+          <t>163445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14352</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36191</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63822</t>
+          <t>66031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1469700</t>
+          <t>1468697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1581797</t>
+          <t>1590158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1464941</t>
+          <t>1466606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1578238</t>
+          <t>1580649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2963721</t>
+          <t>2969696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3127454</t>
+          <t>3123921</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,95%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>874147</t>
+          <t>871841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>976032</t>
+          <t>978258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>832271</t>
+          <t>832167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>931112</t>
+          <t>931160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1726980</t>
+          <t>1729773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1869982</t>
+          <t>1872562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>544797</t>
+          <t>543153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>631452</t>
+          <t>626235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>580551</t>
+          <t>580445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>672868</t>
+          <t>670218</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1156129</t>
+          <t>1149590</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1282603</t>
+          <t>1278501</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>174680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>232141</t>
+          <t>232339</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>259061</t>
+          <t>255708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322382</t>
+          <t>323884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449361</t>
+          <t>449547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>534974</t>
+          <t>537570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49099</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83052</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81270</t>
+          <t>80620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>121550</t>
+          <t>122136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2012</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>369870</t>
+          <t>369401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>434791</t>
+          <t>433861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>479037</t>
+          <t>478251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>547705</t>
+          <t>552678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>868424</t>
+          <t>866703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>962929</t>
+          <t>963259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>235832</t>
+          <t>237510</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>294626</t>
+          <t>296477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383858</t>
+          <t>384944</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>449942</t>
+          <t>451677</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>641011</t>
+          <t>637413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>724638</t>
+          <t>729558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>207081</t>
+          <t>205273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>261925</t>
+          <t>260971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>238734</t>
+          <t>237834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300435</t>
+          <t>297397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>462911</t>
+          <t>457687</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>545113</t>
+          <t>541804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41614</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73538</t>
+          <t>73076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73933</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113605</t>
+          <t>113257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123163</t>
+          <t>124788</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173619</t>
+          <t>171748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>52752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>39471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66739</t>
+          <t>69537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>914487</t>
+          <t>914913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1001366</t>
+          <t>1001556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>729146</t>
+          <t>726609</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1666203</t>
+          <t>1659287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1792335</t>
+          <t>1787556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541683</t>
+          <t>542852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625418</t>
+          <t>623339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>498827</t>
+          <t>495896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>577773</t>
+          <t>575608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1058077</t>
+          <t>1061483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1178520</t>
+          <t>1173029</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275490</t>
+          <t>275519</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342547</t>
+          <t>344558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>292874</t>
+          <t>290570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>357648</t>
+          <t>357278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>591156</t>
+          <t>589689</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>680107</t>
+          <t>683852</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>69953</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108669</t>
+          <t>108539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59333</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97816</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141029</t>
+          <t>137630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191412</t>
+          <t>191690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62849</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53077</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>88329</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229716</t>
+          <t>233110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277273</t>
+          <t>277202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221664</t>
+          <t>223053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>266520</t>
+          <t>265526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>466559</t>
+          <t>463644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>528883</t>
+          <t>529399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,59%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111659</t>
+          <t>109850</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150879</t>
+          <t>150057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123717</t>
+          <t>122060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>163178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246087</t>
+          <t>245907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301255</t>
+          <t>302011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52428</t>
+          <t>53216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89085</t>
+          <t>88295</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35264</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63559</t>
+          <t>63050</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94753</t>
+          <t>98105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140169</t>
+          <t>141240</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>11185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>45370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21604</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1557284</t>
+          <t>1556614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1679658</t>
+          <t>1676207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1467038</t>
+          <t>1470872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1585095</t>
+          <t>1593285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3059707</t>
+          <t>3057697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3219824</t>
+          <t>3223627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>919133</t>
+          <t>921181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1033481</t>
+          <t>1027323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1044797</t>
+          <t>1039669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1155370</t>
+          <t>1154488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1992501</t>
+          <t>1990113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2150255</t>
+          <t>2146097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>561040</t>
+          <t>566184</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>659170</t>
+          <t>659599</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>594419</t>
+          <t>595578</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>689621</t>
+          <t>686654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1183454</t>
+          <t>1183817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1324498</t>
+          <t>1318156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131671</t>
+          <t>133064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>183818</t>
+          <t>184422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>160263</t>
+          <t>158775</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214254</t>
+          <t>216422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>308637</t>
+          <t>309531</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>383118</t>
+          <t>386192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>64182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73620</t>
+          <t>73042</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110926</t>
+          <t>113271</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114353</t>
+          <t>115387</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159963</t>
+          <t>163164</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2016</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>262241</t>
+          <t>258856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>314380</t>
+          <t>314763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308767</t>
+          <t>307743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370591</t>
+          <t>370693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>584069</t>
+          <t>587102</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>669000</t>
+          <t>665165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183759</t>
+          <t>183213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231238</t>
+          <t>232824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240330</t>
+          <t>244255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298880</t>
+          <t>301499</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440491</t>
+          <t>438614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514898</t>
+          <t>517175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>158901</t>
+          <t>160715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>204070</t>
+          <t>204135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217488</t>
+          <t>217475</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>272984</t>
+          <t>274707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>391360</t>
+          <t>389045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>462743</t>
+          <t>459080</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37639</t>
+          <t>38044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79868</t>
+          <t>77541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120499</t>
+          <t>118854</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126229</t>
+          <t>125724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174793</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28122</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>55529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>55355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88675</t>
+          <t>90438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>802069</t>
+          <t>800504</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>893656</t>
+          <t>892050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>769766</t>
+          <t>770531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>856471</t>
+          <t>853233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1592822</t>
+          <t>1596773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1720323</t>
+          <t>1720788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>543361</t>
+          <t>546526</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623278</t>
+          <t>625256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565452</t>
+          <t>569751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652655</t>
+          <t>646032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1142997</t>
+          <t>1139394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1258118</t>
+          <t>1255759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>425287</t>
+          <t>432063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>505149</t>
+          <t>507805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359468</t>
+          <t>357752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>430444</t>
+          <t>427341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>805244</t>
+          <t>809345</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>911932</t>
+          <t>910616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110591</t>
+          <t>111211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156744</t>
+          <t>156123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>119302</t>
+          <t>118747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164123</t>
+          <t>163637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241127</t>
+          <t>242024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308803</t>
+          <t>305356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49548</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>40192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50271</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>83470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>244456</t>
+          <t>246216</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>293664</t>
+          <t>295122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253870</t>
+          <t>254943</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>299601</t>
+          <t>301065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>511817</t>
+          <t>514024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>580976</t>
+          <t>579570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148903</t>
+          <t>148619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194480</t>
+          <t>195054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124949</t>
+          <t>125867</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166590</t>
+          <t>167814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287311</t>
+          <t>288360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349660</t>
+          <t>349020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57339</t>
+          <t>56628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>90622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63661</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97041</t>
+          <t>97226</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>127485</t>
+          <t>130407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174108</t>
+          <t>174449</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>35754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44670</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41137</t>
+          <t>40876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70462</t>
+          <t>71133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>15678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>32526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1346522</t>
+          <t>1342865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1464931</t>
+          <t>1456767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1368338</t>
+          <t>1370977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1489297</t>
+          <t>1483829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2736775</t>
+          <t>2747086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2916817</t>
+          <t>2913348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,28%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>914454</t>
+          <t>914567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1015925</t>
+          <t>1022810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>966231</t>
+          <t>976149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1081740</t>
+          <t>1088169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1910800</t>
+          <t>1916829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2073616</t>
+          <t>2072298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>670833</t>
+          <t>672231</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>772607</t>
+          <t>766484</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>669365</t>
+          <t>670684</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>767747</t>
+          <t>765946</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1368143</t>
+          <t>1364986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1508024</t>
+          <t>1503321</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179738</t>
+          <t>179410</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>236577</t>
+          <t>237922</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239215</t>
+          <t>238247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>305913</t>
+          <t>300896</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>438950</t>
+          <t>437992</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>525849</t>
+          <t>527521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>57496</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>92690</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>64387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103041</t>
+          <t>103508</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137096</t>
+          <t>132778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185239</t>
+          <t>183720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2023</t>
+          <t>Población según la frecuencia de recibir elogios y reconocimientos cuando hago bien mi trabajo en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>196238</t>
+          <t>193251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237430</t>
+          <t>237403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275053</t>
+          <t>274314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>315393</t>
+          <t>316927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>481330</t>
+          <t>479393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>541136</t>
+          <t>537476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129071</t>
+          <t>127508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167426</t>
+          <t>166418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195190</t>
+          <t>193974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231003</t>
+          <t>229669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333015</t>
+          <t>333530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>385234</t>
+          <t>386562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80595</t>
+          <t>81102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111697</t>
+          <t>110919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132105</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166163</t>
+          <t>167483</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>220369</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>267870</t>
+          <t>267443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,47 +9964,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>69383</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>58439</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>82563</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>9,28%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>69383</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>57579</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81988</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88886</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122098</t>
+          <t>121829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55510</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1187971</t>
+          <t>1190473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1607721</t>
+          <t>1630799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>761621</t>
+          <t>753260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1195175</t>
+          <t>1200452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2109585</t>
+          <t>2067159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2724747</t>
+          <t>2697964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436769</t>
+          <t>448653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728791</t>
+          <t>728414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>669454</t>
+          <t>668765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1188693</t>
+          <t>1237651</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237998</t>
+          <t>1246285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1878033</t>
+          <t>1954925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144647</t>
+          <t>148995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248407</t>
+          <t>247843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,82 +10533,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>216090</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>158314</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>252306</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>425364</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>347130</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>491307</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>10,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>216090</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>160708</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>251792</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>425364</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>337337</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>481156</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>106759</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68516</t>
+          <t>68831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118296</t>
+          <t>117548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138671</t>
+          <t>141538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208916</t>
+          <t>208697</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51856</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43020</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53072</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89086</t>
+          <t>87747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>350011</t>
+          <t>350480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>400494</t>
+          <t>402619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>370470</t>
+          <t>371275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413357</t>
+          <t>412896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>735682</t>
+          <t>736547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>804350</t>
+          <t>802886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157809</t>
+          <t>157475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203581</t>
+          <t>202474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157488</t>
+          <t>159319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197729</t>
+          <t>195921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>327495</t>
+          <t>324399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386725</t>
+          <t>383525</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>42460</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>72477</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>44119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93232</t>
+          <t>95443</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134648</t>
+          <t>136390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18497</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>34533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23407</t>
+          <t>22766</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>32847</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1775896</t>
+          <t>1773360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2242955</t>
+          <t>2268169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1460426</t>
+          <t>1389803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1884929</t>
+          <t>1879738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3348146</t>
+          <t>3362770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3979695</t>
+          <t>4002081</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>751604</t>
+          <t>735560</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1052260</t>
+          <t>1058061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1053598</t>
+          <t>1057448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1634294</t>
+          <t>1714593</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1963278</t>
+          <t>1961273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2676044</t>
+          <t>2717537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>284757</t>
+          <t>282918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>408156</t>
+          <t>406446</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>338876</t>
+          <t>346169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>465046</t>
+          <t>465784</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>673650</t>
+          <t>679387</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>851180</t>
+          <t>848156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102733</t>
+          <t>101725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>164091</t>
+          <t>162707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154312</t>
+          <t>153756</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218199</t>
+          <t>218806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>277324</t>
+          <t>267555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>367019</t>
+          <t>363049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89528</t>
+          <t>89943</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78372</t>
+          <t>78128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>112973</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>157588</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P5703-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P5703-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372289</t>
+          <t>370956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>432791</t>
+          <t>430825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>470092</t>
+          <t>467272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>535834</t>
+          <t>539194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>859428</t>
+          <t>857220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>956722</t>
+          <t>951952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271417</t>
+          <t>269538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327500</t>
+          <t>325596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304279</t>
+          <t>301689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>367263</t>
+          <t>367671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587909</t>
+          <t>591108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>676000</t>
+          <t>680043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200295</t>
+          <t>201155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252398</t>
+          <t>252881</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>264993</t>
+          <t>264615</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>324929</t>
+          <t>324646</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>481202</t>
+          <t>479363</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>563371</t>
+          <t>561699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81180</t>
+          <t>78678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119429</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>124054</t>
+          <t>123333</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>169122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212733</t>
+          <t>212196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>272188</t>
+          <t>272248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51134</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34141</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>801028</t>
+          <t>801177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>882748</t>
+          <t>883238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>712754</t>
+          <t>709225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>789575</t>
+          <t>791442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1533729</t>
+          <t>1530752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1649228</t>
+          <t>1651747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>441168</t>
+          <t>441546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516161</t>
+          <t>515285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>379801</t>
+          <t>381312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>450005</t>
+          <t>451381</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>843230</t>
+          <t>842445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>943611</t>
+          <t>943955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>241901</t>
+          <t>243681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>303620</t>
+          <t>307122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>248247</t>
+          <t>248575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>308786</t>
+          <t>309631</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>507284</t>
+          <t>513365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>594815</t>
+          <t>600983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66336</t>
+          <t>66970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101795</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99977</t>
+          <t>98737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141617</t>
+          <t>142136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173665</t>
+          <t>173350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229860</t>
+          <t>229743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26890</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15894</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38552</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57244</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258447</t>
+          <t>255991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>306146</t>
+          <t>303553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>244131</t>
+          <t>244156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>287181</t>
+          <t>287616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>514659</t>
+          <t>512358</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>582232</t>
+          <t>577104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,24%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125381</t>
+          <t>127712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167270</t>
+          <t>172612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111885</t>
+          <t>111281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>150395</t>
+          <t>150380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245643</t>
+          <t>249215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308048</t>
+          <t>307018</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71153</t>
+          <t>72003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107733</t>
+          <t>107165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69118</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>119626</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>163445</t>
+          <t>163509</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>39025</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66031</t>
+          <t>65090</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21940</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1468697</t>
+          <t>1471327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1590158</t>
+          <t>1582269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1466606</t>
+          <t>1464020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1580649</t>
+          <t>1570678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2969696</t>
+          <t>2965820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3123921</t>
+          <t>3126318</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>871841</t>
+          <t>869193</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>978258</t>
+          <t>974464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>832167</t>
+          <t>829133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>931160</t>
+          <t>932385</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1729773</t>
+          <t>1728190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1872562</t>
+          <t>1873335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>543153</t>
+          <t>543846</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>626235</t>
+          <t>629041</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>580445</t>
+          <t>583503</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>670218</t>
+          <t>677694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1149590</t>
+          <t>1153531</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1278501</t>
+          <t>1289580</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174680</t>
+          <t>177656</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>232339</t>
+          <t>234715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>255708</t>
+          <t>255772</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323884</t>
+          <t>320247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449547</t>
+          <t>448058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>537570</t>
+          <t>540516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25258</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50635</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49099</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122136</t>
+          <t>121642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>369401</t>
+          <t>369775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>433861</t>
+          <t>435351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>478251</t>
+          <t>478702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>552678</t>
+          <t>546602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>866703</t>
+          <t>868159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>963259</t>
+          <t>962583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237510</t>
+          <t>239465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296477</t>
+          <t>296439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384944</t>
+          <t>385136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>451677</t>
+          <t>453605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>637413</t>
+          <t>641556</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729558</t>
+          <t>728683</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>205273</t>
+          <t>207997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260971</t>
+          <t>262579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237834</t>
+          <t>242048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>297397</t>
+          <t>302192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>457687</t>
+          <t>460757</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>541804</t>
+          <t>539988</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42451</t>
+          <t>43341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73076</t>
+          <t>75172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74612</t>
+          <t>73674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113257</t>
+          <t>111598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124788</t>
+          <t>123809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171748</t>
+          <t>171527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39471</t>
+          <t>40155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>67713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>914913</t>
+          <t>915031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1001556</t>
+          <t>1004828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>726609</t>
+          <t>729218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>813507</t>
+          <t>815180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1659287</t>
+          <t>1670360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1787556</t>
+          <t>1793343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542852</t>
+          <t>541024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>623339</t>
+          <t>622727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>495896</t>
+          <t>498575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575608</t>
+          <t>580321</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061483</t>
+          <t>1059800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1173029</t>
+          <t>1175214</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>275519</t>
+          <t>279556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344558</t>
+          <t>345797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290570</t>
+          <t>290534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>357278</t>
+          <t>359849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>589689</t>
+          <t>582143</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>683852</t>
+          <t>684787</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69953</t>
+          <t>69745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108539</t>
+          <t>108258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61164</t>
+          <t>60521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97721</t>
+          <t>95660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137630</t>
+          <t>139994</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191690</t>
+          <t>191801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61782</t>
+          <t>63110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88329</t>
+          <t>88352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>233110</t>
+          <t>228535</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277202</t>
+          <t>275520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>223053</t>
+          <t>221473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>265526</t>
+          <t>266081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>463644</t>
+          <t>465974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>529399</t>
+          <t>529795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109850</t>
+          <t>112542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150057</t>
+          <t>151738</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>123514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>163178</t>
+          <t>165369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245907</t>
+          <t>244403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>302011</t>
+          <t>301198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53216</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88295</t>
+          <t>86681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63050</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>97879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141240</t>
+          <t>143353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7981</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45370</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>22243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1556614</t>
+          <t>1558771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1676207</t>
+          <t>1680342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1470872</t>
+          <t>1467768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1593285</t>
+          <t>1593009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3057697</t>
+          <t>3049721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3223627</t>
+          <t>3215313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>921181</t>
+          <t>919484</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1027323</t>
+          <t>1034574</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1039669</t>
+          <t>1036614</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1154488</t>
+          <t>1154696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1990113</t>
+          <t>2001330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2146097</t>
+          <t>2158160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>566184</t>
+          <t>568411</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>659599</t>
+          <t>660275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>595578</t>
+          <t>596953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>686654</t>
+          <t>692643</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1183817</t>
+          <t>1190110</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1318156</t>
+          <t>1322412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133064</t>
+          <t>134643</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>184422</t>
+          <t>185584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>158775</t>
+          <t>160199</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216422</t>
+          <t>215928</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>309531</t>
+          <t>309282</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>386192</t>
+          <t>383256</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>64463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73042</t>
+          <t>73038</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113271</t>
+          <t>110183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115387</t>
+          <t>114952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163164</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>258856</t>
+          <t>258526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>314763</t>
+          <t>312605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>307743</t>
+          <t>312097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370693</t>
+          <t>371409</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587102</t>
+          <t>587465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>665165</t>
+          <t>665574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183213</t>
+          <t>183721</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>232824</t>
+          <t>231113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244255</t>
+          <t>240617</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301499</t>
+          <t>299824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>438614</t>
+          <t>441610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>517175</t>
+          <t>516887</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160715</t>
+          <t>157670</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>204135</t>
+          <t>202731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217475</t>
+          <t>216219</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>274707</t>
+          <t>274119</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>389045</t>
+          <t>389985</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>459080</t>
+          <t>464550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65123</t>
+          <t>65273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77541</t>
+          <t>78522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118854</t>
+          <t>120024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125724</t>
+          <t>126622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>170832</t>
+          <t>176128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>43047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55529</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55355</t>
+          <t>55833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>91157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>800504</t>
+          <t>798664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>892050</t>
+          <t>890075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>770531</t>
+          <t>769986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>853233</t>
+          <t>857508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1596773</t>
+          <t>1585666</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1720788</t>
+          <t>1719998</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546526</t>
+          <t>546576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>625256</t>
+          <t>632160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>569751</t>
+          <t>566128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>646032</t>
+          <t>650155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1139394</t>
+          <t>1138398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255759</t>
+          <t>1255135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432063</t>
+          <t>425646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>507805</t>
+          <t>504664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>357752</t>
+          <t>359305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>427341</t>
+          <t>431000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>809345</t>
+          <t>806243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>910616</t>
+          <t>917100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>111211</t>
+          <t>112721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156123</t>
+          <t>160463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,82 +7687,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>139783</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>120300</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>164182</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>273277</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>241409</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>305997</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>7,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>139783</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>118747</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>163637</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>273277</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>242024</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>305356</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>50986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,47 +7835,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>65154</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>50188</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>82423</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>2,03%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>65154</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>50037</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>83470</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>245294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>295122</t>
+          <t>292768</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>254943</t>
+          <t>253783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>301065</t>
+          <t>299662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>514024</t>
+          <t>511972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>579570</t>
+          <t>579218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148619</t>
+          <t>151058</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195054</t>
+          <t>196946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125867</t>
+          <t>124699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167814</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>288360</t>
+          <t>287129</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>349020</t>
+          <t>349242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56628</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>91051</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>63323</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97226</t>
+          <t>97691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130407</t>
+          <t>129144</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174449</t>
+          <t>177947</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14443</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35754</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40876</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>70169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32526</t>
+          <t>32930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1342865</t>
+          <t>1348365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1456767</t>
+          <t>1458394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1370977</t>
+          <t>1371501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1483829</t>
+          <t>1487096</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2747086</t>
+          <t>2744607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2913348</t>
+          <t>2913673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>914567</t>
+          <t>912851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1022810</t>
+          <t>1017545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976149</t>
+          <t>968857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1088169</t>
+          <t>1078452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1916829</t>
+          <t>1913179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2072298</t>
+          <t>2068725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>672231</t>
+          <t>673199</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>766484</t>
+          <t>771678</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>670684</t>
+          <t>667327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>765946</t>
+          <t>768274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1364986</t>
+          <t>1371735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1503321</t>
+          <t>1508656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>179410</t>
+          <t>178575</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>237922</t>
+          <t>235334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238247</t>
+          <t>239374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>300896</t>
+          <t>305328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>437992</t>
+          <t>432653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>527521</t>
+          <t>522587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>58678</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>95672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64387</t>
+          <t>65983</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>103508</t>
+          <t>103013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132778</t>
+          <t>132083</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183720</t>
+          <t>184905</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>215086</t>
+          <t>239021</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>193251</t>
+          <t>216023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237403</t>
+          <t>262998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>294642</t>
+          <t>314444</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>274314</t>
+          <t>291919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>316927</t>
+          <t>335405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>509729</t>
+          <t>553465</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>479393</t>
+          <t>523165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>537476</t>
+          <t>584362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>147052</t>
+          <t>162928</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>127508</t>
+          <t>143573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166418</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>211693</t>
+          <t>235829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193974</t>
+          <t>215073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229669</t>
+          <t>255728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>358746</t>
+          <t>398757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333530</t>
+          <t>369852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386562</t>
+          <t>425736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95175</t>
+          <t>112815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81102</t>
+          <t>97018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147460</t>
+          <t>156625</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131929</t>
+          <t>138934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167483</t>
+          <t>172600</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>242635</t>
+          <t>269440</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>220821</t>
+          <t>246483</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>267443</t>
+          <t>296735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47083</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69383</t>
+          <t>77564</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58439</t>
+          <t>63956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82563</t>
+          <t>92548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>103758</t>
+          <t>116173</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>100070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121829</t>
+          <t>134954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27876</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>37225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43729</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>39444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55656</t>
+          <t>61053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511005</t>
+          <t>574511</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511005</t>
+          <t>574511</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511005</t>
+          <t>574511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>747591</t>
+          <t>812486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>747591</t>
+          <t>812486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>747591</t>
+          <t>812486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1258596</t>
+          <t>1386997</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1258596</t>
+          <t>1386997</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1258596</t>
+          <t>1386997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1321910</t>
+          <t>1140125</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1190473</t>
+          <t>1086898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1630799</t>
+          <t>1195245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1055092</t>
+          <t>1060839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>753260</t>
+          <t>1012861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1200452</t>
+          <t>1101321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2377002</t>
+          <t>2200964</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2067159</t>
+          <t>2127664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2697964</t>
+          <t>2270676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>635748</t>
+          <t>712993</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448653</t>
+          <t>661919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728414</t>
+          <t>763436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>833813</t>
+          <t>712612</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668765</t>
+          <t>675650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1237651</t>
+          <t>751132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1469561</t>
+          <t>1425605</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1246285</t>
+          <t>1366357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1954925</t>
+          <t>1488395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>209273</t>
+          <t>239244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148995</t>
+          <t>210741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>247843</t>
+          <t>273688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>216090</t>
+          <t>240342</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>158314</t>
+          <t>214859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>252306</t>
+          <t>265963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>425364</t>
+          <t>479586</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>347130</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>491307</t>
+          <t>523491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>93351</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>76228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>113972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94629</t>
+          <t>106308</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68831</t>
+          <t>88375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117548</t>
+          <t>127118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>176788</t>
+          <t>199659</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>141538</t>
+          <t>175033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>230760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22935</t>
+          <t>27835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50918</t>
+          <t>56312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>69562</t>
+          <t>85513</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50732</t>
+          <t>69156</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87747</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2285985</t>
+          <t>2226009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2285985</t>
+          <t>2226009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2285985</t>
+          <t>2226009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2232291</t>
+          <t>2165319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2232291</t>
+          <t>2165319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2232291</t>
+          <t>2165319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4518276</t>
+          <t>4391327</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4518276</t>
+          <t>4391327</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4518276</t>
+          <t>4391327</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>376167</t>
+          <t>407381</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>350480</t>
+          <t>379235</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402619</t>
+          <t>438151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>392898</t>
+          <t>432267</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371275</t>
+          <t>407959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>412896</t>
+          <t>455719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>769065</t>
+          <t>839648</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>736547</t>
+          <t>804710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>802886</t>
+          <t>875018</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>179159</t>
+          <t>203046</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157475</t>
+          <t>177161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202474</t>
+          <t>227810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>176045</t>
+          <t>198427</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159319</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195921</t>
+          <t>220349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>355204</t>
+          <t>401473</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324399</t>
+          <t>369932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383525</t>
+          <t>432286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>61055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42460</t>
+          <t>46853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72477</t>
+          <t>78300</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56799</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44119</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>80424</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>112784</t>
+          <t>123836</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95443</t>
+          <t>104827</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>136390</t>
+          <t>148094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18278</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>43783</t>
+          <t>49550</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>37492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58201</t>
+          <t>65145</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22766</t>
+          <t>29727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,27 +11456,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32847</t>
+          <t>38244</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>644057</t>
+          <t>708782</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644057</t>
+          <t>708782</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>644057</t>
+          <t>708782</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659204</t>
+          <t>732203</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>659204</t>
+          <t>732203</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>659204</t>
+          <t>732203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1303261</t>
+          <t>1440984</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1303261</t>
+          <t>1440984</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1303261</t>
+          <t>1440984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1913163</t>
+          <t>1786527</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1773360</t>
+          <t>1724695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2268169</t>
+          <t>1846953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1742632</t>
+          <t>1807551</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1389803</t>
+          <t>1758190</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1879738</t>
+          <t>1864602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3655796</t>
+          <t>3594078</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3362770</t>
+          <t>3504369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4002081</t>
+          <t>3677737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>961959</t>
+          <t>1078968</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>735560</t>
+          <t>1020974</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1058061</t>
+          <t>1135924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1221551</t>
+          <t>1146868</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1057448</t>
+          <t>1102869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1714593</t>
+          <t>1200655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2183510</t>
+          <t>2225836</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1961273</t>
+          <t>2148339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2717537</t>
+          <t>2304726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>360433</t>
+          <t>413114</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282918</t>
+          <t>376907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>406446</t>
+          <t>458754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>420349</t>
+          <t>459748</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>346169</t>
+          <t>424450</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>465784</t>
+          <t>489758</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>780783</t>
+          <t>872862</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679387</t>
+          <t>823500</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>848156</t>
+          <t>929696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>134960</t>
+          <t>151962</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101725</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162707</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>189369</t>
+          <t>213419</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153756</t>
+          <t>190214</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218806</t>
+          <t>238697</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>324329</t>
+          <t>365382</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>267555</t>
+          <t>328830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>363049</t>
+          <t>401866</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>70532</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52155</t>
+          <t>62109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>89943</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>82422</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51147</t>
+          <t>68254</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>99863</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>135715</t>
+          <t>161152</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112973</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>186593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3441048</t>
+          <t>3509301</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3441048</t>
+          <t>3509301</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3441048</t>
+          <t>3509301</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3639085</t>
+          <t>3710008</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3639085</t>
+          <t>3710008</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3639085</t>
+          <t>3710008</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7080133</t>
+          <t>7219309</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7080133</t>
+          <t>7219309</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7080133</t>
+          <t>7219309</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
